--- a/data/trans_bre/IQ2605_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IQ2605_R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>4,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 19,42</t>
+          <t>-10,67; 18,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 15,92</t>
+          <t>-16,03; 13,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 17,1</t>
+          <t>-7,2; 18,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 32,26</t>
+          <t>-23,45; 34,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,48; 57,13</t>
+          <t>-21,2; 58,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 33,61</t>
+          <t>-25,26; 29,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 25,93</t>
+          <t>-9,09; 28,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-48,6; 117,75</t>
+          <t>-48,83; 122,49</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-7,12</t>
+          <t>-10,64</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-10,04%</t>
+          <t>-15,28%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 14,37</t>
+          <t>-7,47; 14,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 16,29</t>
+          <t>-2,19; 16,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 7,98</t>
+          <t>-7,25; 8,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,96; 17,28</t>
+          <t>-35,82; 14,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 37,1</t>
+          <t>-15,55; 38,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 25,13</t>
+          <t>-2,65; 24,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 9,5</t>
+          <t>-8,1; 9,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 30,25</t>
+          <t>-45,14; 25,87</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,05</t>
+          <t>-3,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-6,73%</t>
+          <t>-4,2%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 24,84</t>
+          <t>-1,6; 24,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 15,45</t>
+          <t>-4,14; 15,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 4,59</t>
+          <t>-23,76; 3,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 18,75</t>
+          <t>-26,49; 20,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 76,41</t>
+          <t>-3,47; 74,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 20,1</t>
+          <t>-4,52; 20,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,4; 8,29</t>
+          <t>-35,36; 6,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,1; 32,12</t>
+          <t>-30,99; 33,91</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-51,52</t>
+          <t>-52,68</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-58,48%</t>
+          <t>-58,69%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 12,92</t>
+          <t>-13,83; 12,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 14,56</t>
+          <t>-5,49; 14,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 2,96</t>
+          <t>-16,9; 1,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-74,71; -19,07</t>
+          <t>-76,53; -22,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 28,0</t>
+          <t>-22,8; 26,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 19,27</t>
+          <t>-6,44; 18,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 3,46</t>
+          <t>-18,28; 1,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,21; -27,18</t>
+          <t>-82,17; -28,08</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,81</t>
+          <t>-2,85</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-6,25%</t>
+          <t>-3,14%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 4,85</t>
+          <t>-28,04; 5,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 9,32</t>
+          <t>-25,03; 9,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 5,54</t>
+          <t>-14,72; 6,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,87; 12,82</t>
+          <t>-20,86; 16,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 8,39</t>
+          <t>-39,58; 9,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 16,96</t>
+          <t>-36,58; 19,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 6,13</t>
+          <t>-15,38; 6,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 14,84</t>
+          <t>-22,39; 19,9</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 9,54</t>
+          <t>-19,35; 9,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 10,8</t>
+          <t>-13,7; 10,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 9,25</t>
+          <t>-21,29; 8,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 21,75</t>
+          <t>-26,79; 23,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,0; 23,75</t>
+          <t>-37,78; 25,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 13,74</t>
+          <t>-15,6; 13,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 14,24</t>
+          <t>-28,34; 12,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,48; 29,29</t>
+          <t>-29,57; 32,45</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 9,06</t>
+          <t>-10,73; 9,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 4,78</t>
+          <t>-14,09; 5,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 8,29</t>
+          <t>-11,54; 7,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 22,69</t>
+          <t>-14,94; 19,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 18,48</t>
+          <t>-18,47; 20,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 6,87</t>
+          <t>-18,41; 8,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 13,69</t>
+          <t>-16,36; 11,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 36,24</t>
+          <t>-17,95; 30,61</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,86</t>
+          <t>6,62</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 9,99</t>
+          <t>-6,83; 10,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 7,72</t>
+          <t>-9,63; 7,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 2,81</t>
+          <t>-9,95; 2,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 17,41</t>
+          <t>-3,33; 16,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 16,04</t>
+          <t>-9,59; 16,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 11,57</t>
+          <t>-12,49; 10,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 3,39</t>
+          <t>-11,39; 3,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 21,82</t>
+          <t>-3,41; 20,9</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-4,45</t>
+          <t>-5,11</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-5,83%</t>
+          <t>-6,69%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 5,37</t>
+          <t>-3,1; 5,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 4,45</t>
+          <t>-3,5; 3,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 0,25</t>
+          <t>-6,86; 0,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 3,92</t>
+          <t>-13,23; 3,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 10,57</t>
+          <t>-5,64; 10,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 6,28</t>
+          <t>-4,65; 5,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 0,31</t>
+          <t>-8,46; 0,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 5,25</t>
+          <t>-16,57; 4,65</t>
         </is>
       </c>
     </row>
